--- a/gemini_epar_analysis.xlsx
+++ b/gemini_epar_analysis.xlsx
@@ -615,7 +615,9 @@
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="n">
+        <v>2013</v>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>Antipsychotic</t>
@@ -678,7 +680,9 @@
           <t>cellulose microcrystalline; crospovidone; hypromellose; magnesium stearate; lactose monohydrate; sodium lauryl sulfate; hydroxypropylcellulose; propylene glycol; titanium dioxide; ferric oxide yellow; ferric oxide red; colloidal silicon dioxide</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="n">
+        <v>2014</v>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -733,7 +737,9 @@
           <t>Squalene; Polysorbate 80; Sorbitan trioleate; Sodium citrate dihydrate; Citric acid monohydrate; Sodium chloride; Potassium chloride; Potassium dihydrogen phosphate; Disodium phosphate dihydrate; Magnesium chloride hexahydrate; Calcium chloride dihydrate; Water for injections</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="n">
+        <v>2010</v>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>Influenza vaccine</t>
@@ -792,7 +798,9 @@
           <t>hydroxypropylbetadex; macrogol (E1521)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="n">
+        <v>2024</v>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
@@ -916,7 +924,9 @@
           <t>microcrystalline cellulose (E460); sucrose lauric acid esters; povidone K-30; croscarmellose sodium; colloidal hydrated silica; sodium stearyl fumarate; magnesium stearate; glycerol monocaprylcaproate (type I); glycerol; polyglyceryl oleate; purified water; butylated hydroxyanisole (E320); gelatin; sorbitol; 1,4-sorbitan; titanium dioxide (E171); yellow iron oxide (E172); red iron oxide (E172); shellac glaze (partially esterified); black iron oxide (E172); propylene glycol (E1520)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="n">
+        <v>2015</v>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -1101,7 +1111,9 @@
           <t>lactose monohydrate; microcrystalline cellulose; sodium starch glycolate (type A); silica colloidal hydrophobic; magnesium stearate; talc; macrogol; polyvinyl alcohol; titanium dioxide</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="n">
+        <v>2018</v>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
@@ -1688,7 +1700,9 @@
           <t>Indigo carmine aluminium lake (E132); Magnesium stearate; Lactose monohydrate</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="n">
+        <v>2013</v>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
           <t>Immunomodulatory agent</t>
@@ -1752,7 +1766,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
@@ -1812,7 +1826,9 @@
           <t>butylhydroxyanisole (E 320); butylhydroxytoluene (E 321); macrogol high-molecular-mass 200K; macrogol high-molecular-mass 5000K; hypromellose 2910; sodium chloride; allura red AC (E 129); magnesium stearate; cellulose acetate; macrogol 3350; hydroxypropylcellulose; poly(vinyl alcohol); titanium dioxide (E 171); talc; indigo carmine (E 132); sunset yellow FCF (E 110); shellac; iron oxide black (E 172); propylene glycol</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="n">
+        <v>2026</v>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
           <t>Treatment of tardive dyskinesia</t>
@@ -2058,7 +2074,9 @@
           <t>Aluminium hydroxide; Sodium chloride; Sucrose; Histidine; Water for Injection</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="n">
+        <v>2013</v>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
           <t>Meningococcal B vaccine</t>
@@ -2377,7 +2395,9 @@
           <t>microcrystalline cellulose; croscarmellose sodium; poloxamer 188; povidone; magnesium stearate; titanium dioxide; iron oxide</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="n">
+        <v>2013</v>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
           <t>Tyrosine kinase inhibitor</t>
@@ -2498,7 +2518,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2562,7 +2582,9 @@
           <t>Lactose monohydrate</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="n">
+        <v>2014</v>
+      </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -2806,7 +2828,9 @@
           <t>microcrystalline cellulose; croscarmellose sodium; sodium lauryl sulphate; colloidal silicon dioxide; magnesium stearate; gelatin; titanium dioxide; shellac glaze; iron oxide black; polypropylene glycol</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="n">
+        <v>2021</v>
+      </c>
       <c r="J38" t="inlineStr">
         <is>
           <t>BTK inhibitor</t>
@@ -3052,7 +3076,9 @@
           <t>Microcrystalline cellulose; Anhydrous lactose; Hydroxypropyl cellulose; Croscarmellose sodium; Colloidal anhydrous silica; Magnesium stearate; Hypromellose 2910; Titanium dioxide (E171); Triacetin; Iron oxide yellow (E172)</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="n">
+        <v>2016</v>
+      </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
@@ -3111,7 +3137,9 @@
           <t>Microcrystalline cellulose; Colloidal anhydrous silica; Partially pregelatinised starch; Magnesium stearate; Sodium starch glycolate; Gelatin; Titanium dioxide; Yellow iron oxide; Indigo carmine; Shellac; Black iron oxide; Propylene glycol; Ammonium hydroxide</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="n">
+        <v>2020</v>
+      </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
@@ -3235,7 +3263,9 @@
           <t>Dibasic calcium phosphate dihydrate; microcrystalline cellulose; crospovidone; povidone; magnesium stearate; hypromellose; polyethylene glycol; titanium dioxide</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="n">
+        <v>2012</v>
+      </c>
       <c r="J45" t="inlineStr">
         <is>
           <t>Tyrosine kinase inhibitor (TKI) / Anticancer medicinal product</t>
@@ -3481,7 +3511,9 @@
           <t>maize starch; magnesium stearate; silica, colloidal anhydrous; water; gelatine; titanium dioxide (E 171); quinoline yellow (E 104); erythrosine (E 127)</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="n">
+        <v>2017</v>
+      </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
@@ -3605,7 +3637,9 @@
           <t>microcrystalline cellulose; anhydrous dibasic calcium phosphate; sodium starch glycolate; magnesium stearate; hypromellose; titanium dioxide; lactose monohydrate; macrogol; triacetin; red iron oxide</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="n">
+        <v>2021</v>
+      </c>
       <c r="J51" t="inlineStr">
         <is>
           <t>Janus kinase (JAK) 1 inhibitor</t>
@@ -3664,7 +3698,9 @@
           <t>trisodium citrate; sodium chloride; L-valine; L-alanine; L-threonine; sucrose</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="n">
+        <v>2011</v>
+      </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
@@ -3770,7 +3806,9 @@
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="n">
+        <v>2012</v>
+      </c>
       <c r="J54" t="inlineStr">
         <is>
           <t>Antibacterial agent</t>
@@ -4259,7 +4297,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1985</v>
+        <v>2019</v>
       </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
@@ -4442,7 +4480,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
@@ -4900,7 +4938,9 @@
           <t>microcrystalline cellulose; pregelatinised starch; hydroxypropyl cellulose; butylated hydroxytoluene; sodium starch glycollate; magnesium stearate; polyvinyl alcohol; titanium dioxide; talc; macrogol; lecithin</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
+      <c r="I72" t="n">
+        <v>2011</v>
+      </c>
       <c r="J72" t="inlineStr">
         <is>
           <t>Antibacterial (macrocycles)</t>
@@ -5325,7 +5365,9 @@
           <t>mannitol; macrogol 6000; microcrystalline cellulose; low substituted hydroxypropylcellulose; maize starch; hydrogenated castor oil; stearic acid; anhydrous colloidal silica; lactose; hypromellose; titanium dioxide; triacetin; yellow iron oxide; red iron oxide; carnauba wax</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr"/>
+      <c r="I79" t="n">
+        <v>2010</v>
+      </c>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
@@ -5555,7 +5597,9 @@
           <t>mannitol; fumaric acid; sodium hydroxide; hydroxypropylcellulose; croscarmellose sodium; microcrystalline cellulose; magnesium stearate</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr"/>
+      <c r="I83" t="n">
+        <v>2011</v>
+      </c>
       <c r="J83" t="inlineStr">
         <is>
           <t>Antihypertensive agent</t>
@@ -5614,7 +5658,9 @@
           <t>povidone; polysorbate 20; lactose monohydrate; croscarmellose sodium; silicified microcrystalline cellulose; magnesium stearate; hypromellose; macrogol; triacetin; titanium dioxide</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr"/>
+      <c r="I84" t="n">
+        <v>2011</v>
+      </c>
       <c r="J84" t="inlineStr">
         <is>
           <t>Antiretroviral</t>
@@ -5803,7 +5849,9 @@
           <t>Lactose</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr"/>
+      <c r="I87" t="n">
+        <v>2011</v>
+      </c>
       <c r="J87" t="inlineStr">
         <is>
           <t>Inhibitor of the coagulation factor Xa (FXa)</t>
@@ -5862,7 +5910,9 @@
           <t>microcrystalline cellulose; magnesium stearate; gelatin; titanium dioxide</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr"/>
+      <c r="I88" t="n">
+        <v>2017</v>
+      </c>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr"/>
@@ -5922,7 +5972,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -6364,7 +6414,9 @@
           <t>microcrystalline cellulose; lactose monohydrate; sodium lauryl sulfate; povidone; sodium starch glycolate (Type A); talc; magnesium stearate; gelatine; iron oxide black (E172); iron oxide red (E172); titanium dioxide (E171); shellac</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr"/>
+      <c r="I96" t="n">
+        <v>2013</v>
+      </c>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr"/>
@@ -6424,7 +6476,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
@@ -6618,7 +6670,9 @@
           <t>pregelatinised starch; dextrin; croscarmellose sodium; hypromellose; magnesium stearate; titanium dioxide; macrogol 400</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr"/>
+      <c r="I100" t="n">
+        <v>2011</v>
+      </c>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr"/>
@@ -6677,7 +6731,9 @@
           <t>microcrystalline cellulose; lactose monohydrate; povidone; pregelatinized starch; polysorbate 20; croscarmellose sodium; magnesium stearate; hypromellose; indigo carmine aluminium lake; macrogol; red iron oxide; sunset yellow aluminium lake; titanium dioxide; triacetin</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr"/>
+      <c r="I101" t="n">
+        <v>2011</v>
+      </c>
       <c r="J101" t="inlineStr">
         <is>
           <t>Antiretroviral</t>
@@ -7753,7 +7809,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -8057,7 +8113,9 @@
           <t>lactose monohydrate; colloidal anhydrous silica; crospovidone type A; saccharin sodium dihydrate; sodium stearyl fumarate</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr"/>
+      <c r="I123" t="n">
+        <v>2019</v>
+      </c>
       <c r="J123" t="inlineStr">
         <is>
           <t>Diagnosis of growth hormone deficiency (GHD)</t>
@@ -8434,7 +8492,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
@@ -8620,7 +8678,9 @@
           <t>Medium-chain triglycerides; Cetalkonium chloride; Glycerol; Tyloxapol; Poloxamer 188; Sodium hydroxide; Water for injections</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr"/>
+      <c r="I132" t="n">
+        <v>2015</v>
+      </c>
       <c r="J132" t="inlineStr">
         <is>
           <t>Immunosuppressant</t>
@@ -9070,7 +9130,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
@@ -9130,7 +9190,9 @@
           <t>microcrystalline cellulose; lactose monohydrate; croscarmellose sodium; magnesium stearate; hypromellose; titanium dioxide; triacetin; red iron oxide</t>
         </is>
       </c>
-      <c r="I140" t="inlineStr"/>
+      <c r="I140" t="n">
+        <v>2012</v>
+      </c>
       <c r="J140" t="inlineStr">
         <is>
           <t>Tyrosine kinase inhibitor</t>
@@ -9194,7 +9256,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr"/>
@@ -9251,7 +9313,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
@@ -9506,7 +9568,9 @@
           <t>cellulose microcrystalline; mannitol; croscarmellose sodium; magnesium stearate; colloidal silicon dioxide; hypromellose; titanium dioxide (E171); macrogol; talc; iron oxide yellow (E172); iron oxide red (E172); iron oxide black (E172)</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr"/>
+      <c r="I146" t="n">
+        <v>2020</v>
+      </c>
       <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr"/>
       <c r="L146" t="inlineStr"/>
@@ -9667,7 +9731,9 @@
           <t>lactose monohydrate; microcrystalline cellulose; sodium starch glycolate; magnesium stearate; stearic acid; colloidal anhydrous silica (colloidal silicon dioxide); hydroxypropyl cellulose; povidone</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr"/>
+      <c r="I149" t="n">
+        <v>2012</v>
+      </c>
       <c r="J149" t="inlineStr">
         <is>
           <t>Selective inhibitor of JAK1 and JAK2</t>
@@ -9925,7 +9991,9 @@
           <t>arginine; copovidone; magnesium stearate; maize starch; colloidal anhydrous silica; hypromellose; titanium dioxide (E171); talc; propylene glycol; iron oxides, yellow and red (E172); iron oxide, red (E172)</t>
         </is>
       </c>
-      <c r="I153" t="inlineStr"/>
+      <c r="I153" t="n">
+        <v>2012</v>
+      </c>
       <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr"/>
@@ -9981,7 +10049,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
@@ -10106,7 +10174,9 @@
           <t>disodium hydrogen citrate; anhydrous monosodium citrate; sodium hydrogen carbonate; sucralose; povidone K25; docusate sodium; mannitol; macrogol 6000; magnesium stearate</t>
         </is>
       </c>
-      <c r="I156" t="inlineStr"/>
+      <c r="I156" t="n">
+        <v>2018</v>
+      </c>
       <c r="J156" t="inlineStr">
         <is>
           <t>Glucocorticosteroid</t>
@@ -10689,7 +10759,9 @@
           <t>Magnesium stearate; Opadry; Lactose monohydrate</t>
         </is>
       </c>
-      <c r="I165" t="inlineStr"/>
+      <c r="I165" t="n">
+        <v>2011</v>
+      </c>
       <c r="J165" t="inlineStr">
         <is>
           <t>Treatment of type 2 diabetes mellitus</t>
@@ -10875,7 +10947,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr"/>
@@ -10928,7 +11000,7 @@
       </c>
       <c r="H169" t="inlineStr"/>
       <c r="I169" t="n">
-        <v>2008</v>
+        <v>2019</v>
       </c>
       <c r="J169" t="inlineStr">
         <is>
@@ -11054,7 +11126,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr"/>
@@ -11094,7 +11166,9 @@
       <c r="F172" t="inlineStr"/>
       <c r="G172" t="inlineStr"/>
       <c r="H172" t="inlineStr"/>
-      <c r="I172" t="inlineStr"/>
+      <c r="I172" t="n">
+        <v>2010</v>
+      </c>
       <c r="J172" t="inlineStr">
         <is>
           <t>Pyrimidine synthesis inhibitor</t>
@@ -11377,7 +11451,9 @@
           <t>microcrystalline cellulose; sodium starch glycolate; magnesium stearate; poly(vinyl alcohol); macrogol (polyethylene glycol); titanium dioxide; talc; brilliant blue FCF aluminium lake</t>
         </is>
       </c>
-      <c r="I177" t="inlineStr"/>
+      <c r="I177" t="n">
+        <v>2022</v>
+      </c>
       <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr"/>
@@ -11501,7 +11577,9 @@
           <t>pregelatinized starch; sodium starch glycolate; microcrystalline cellulose; lactose monohydrate; silica, colloidal anhydrous; magnesium stearate; gelatin; titanium dioxide; red iron oxide; shellac; black iron oxide; propylene glycol</t>
         </is>
       </c>
-      <c r="I179" t="inlineStr"/>
+      <c r="I179" t="n">
+        <v>2013</v>
+      </c>
       <c r="J179" t="inlineStr">
         <is>
           <t>Lipid-lowering drug</t>
@@ -11813,7 +11891,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J184" t="inlineStr">
         <is>
@@ -12435,7 +12513,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="J194" t="inlineStr">
         <is>
@@ -12500,7 +12578,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr"/>
@@ -12682,7 +12760,9 @@
           <t>Sucrose; Potassium dihydrogen phosphate; Sodium chloride; Sodium dihydrogen phosphate monohydrate; Disodium phosphate dihydrate</t>
         </is>
       </c>
-      <c r="I198" t="inlineStr"/>
+      <c r="I198" t="n">
+        <v>2010</v>
+      </c>
       <c r="J198" t="inlineStr">
         <is>
           <t>Meningococcal Group A, C, W135 and Y Conjugate Vaccine</t>
@@ -12741,7 +12821,9 @@
           <t>Water for injections</t>
         </is>
       </c>
-      <c r="I199" t="inlineStr"/>
+      <c r="I199" t="n">
+        <v>2011</v>
+      </c>
       <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr"/>
       <c r="L199" t="inlineStr"/>
@@ -13007,7 +13089,9 @@
           <t>Microcrystalline cellulose; Lactose monohydrate; Croscarmellose sodium; Sodium lauryl sulphate; Colloidal silicon dioxide; Magnesium stearate; Carnauba wax; Hypromellose acetate succinate (HPMCAS); Opadry II Blue; Opacode Black</t>
         </is>
       </c>
-      <c r="I203" t="inlineStr"/>
+      <c r="I203" t="n">
+        <v>2012</v>
+      </c>
       <c r="J203" t="inlineStr"/>
       <c r="K203" t="inlineStr">
         <is>
@@ -13204,7 +13288,9 @@
           <t>mannitol; microcrystalline cellulose; magnesium oxide; sodium lauryl sulfate; hydroxypropylcellulose; carmellose calcium; magnesium stearate; hypromellose; titanium dioxide; triethyl citrate; talc; red ferric oxide (E172)</t>
         </is>
       </c>
-      <c r="I206" t="inlineStr"/>
+      <c r="I206" t="n">
+        <v>2019</v>
+      </c>
       <c r="J206" t="inlineStr">
         <is>
           <t>TPO receptor agonist</t>
@@ -13641,7 +13727,9 @@
           <t>Acetic acid; Ammonium sulphate; Carbomer 980; Di-sodium hydrogen phosphate, anhydrous; Sodium hydroxide; Water for injections</t>
         </is>
       </c>
-      <c r="I213" t="inlineStr"/>
+      <c r="I213" t="n">
+        <v>2012</v>
+      </c>
       <c r="J213" t="inlineStr"/>
       <c r="K213" t="inlineStr"/>
       <c r="L213" t="inlineStr"/>
@@ -13773,7 +13861,9 @@
           <t>Lactose monohydrate; Microcrystalline cellulose; Sodium starch glycolate (Type A); Hydroxy propyl cellulose; Magnesium stearate; Anhydrous colloidal silica; Partially hydrolysed poly(vinyl alcohol); Talc; Titanium dioxide; Macrogol 4000</t>
         </is>
       </c>
-      <c r="I215" t="inlineStr"/>
+      <c r="I215" t="n">
+        <v>2020</v>
+      </c>
       <c r="J215" t="inlineStr"/>
       <c r="K215" t="inlineStr"/>
       <c r="L215" t="inlineStr"/>
@@ -13828,7 +13918,9 @@
           <t>Sucrose; Trometamol; Sodium chloride; Water for injections</t>
         </is>
       </c>
-      <c r="I216" t="inlineStr"/>
+      <c r="I216" t="n">
+        <v>2012</v>
+      </c>
       <c r="J216" t="inlineStr">
         <is>
           <t>Meningococcal vaccine</t>
@@ -14078,7 +14170,9 @@
           <t>ascorbic acid; mannitol; sucrose; hydrochloric acid; sodium hydroxide</t>
         </is>
       </c>
-      <c r="I220" t="inlineStr"/>
+      <c r="I220" t="n">
+        <v>2022</v>
+      </c>
       <c r="J220" t="inlineStr"/>
       <c r="K220" t="inlineStr"/>
       <c r="L220" t="inlineStr"/>
@@ -14317,7 +14411,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>2018</v>
+        <v>2024</v>
       </c>
       <c r="J224" t="inlineStr">
         <is>
@@ -14442,7 +14536,9 @@
           <t>Poloxamer; Sodium lauryl sulfate; Crospovidone; Magnesium stearate; Colloidal anhydrous silica; Lactose; Gelatin</t>
         </is>
       </c>
-      <c r="I226" t="inlineStr"/>
+      <c r="I226" t="n">
+        <v>2015</v>
+      </c>
       <c r="J226" t="inlineStr"/>
       <c r="K226" t="inlineStr"/>
       <c r="L226" t="inlineStr"/>
@@ -14501,7 +14597,9 @@
           <t>Medium-chain triglycerides; Hard fat; Lecithin; Gelatin; Glycerol (85 %); Titanium dioxide; Iron oxide red; Iron oxide yellow; Shellac glaze; Iron oxide black; Propylene glycol</t>
         </is>
       </c>
-      <c r="I227" t="inlineStr"/>
+      <c r="I227" t="n">
+        <v>2015</v>
+      </c>
       <c r="J227" t="inlineStr"/>
       <c r="K227" t="inlineStr"/>
       <c r="L227" t="inlineStr"/>
@@ -14748,7 +14846,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="J231" t="inlineStr">
         <is>
@@ -15316,7 +15414,9 @@
           <t>microcrystalline cellulose; croscarmellose sodium; hypromellose acetate succinate; povidone K30; sodium laurilsulfate; magnesium stearate; polyvinyl alcohol; titanium dioxide (E171); macrogol 3350; talc; carmine (E120); brilliant blue FCF aluminum lake (E133); indigo carmine aluminum lake (E132); shellac; iron oxide black (E172); propylene glycol; ammonium hydroxide; carnauba wax</t>
         </is>
       </c>
-      <c r="I240" t="inlineStr"/>
+      <c r="I240" t="n">
+        <v>2015</v>
+      </c>
       <c r="J240" t="inlineStr">
         <is>
           <t>CFTR corrector and potentiator</t>
@@ -15571,7 +15671,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="J244" t="inlineStr"/>
       <c r="K244" t="inlineStr"/>
@@ -15688,7 +15788,9 @@
           <t>disodium phosphate dihydrate; propylene glycol; phenol; hydrochloric acid; sodium hydroxide; water for injections</t>
         </is>
       </c>
-      <c r="I246" t="inlineStr"/>
+      <c r="I246" t="n">
+        <v>2018</v>
+      </c>
       <c r="J246" t="inlineStr">
         <is>
           <t>GLP-1 receptor agonist</t>
@@ -15812,7 +15914,9 @@
           <t>partially pregelatinised maize starch; microcrystalline cellulose; colloidal silicon dioxide; magnesium stearate; hydroxypropyl methyl cellulose</t>
         </is>
       </c>
-      <c r="I248" t="inlineStr"/>
+      <c r="I248" t="n">
+        <v>2020</v>
+      </c>
       <c r="J248" t="inlineStr">
         <is>
           <t>Treatment of peanut allergy</t>
@@ -16005,7 +16109,9 @@
           <t>LM pectin; sucrose; phenylethyl alcohol; propyl parahydroxybenzoate (propylparaben)</t>
         </is>
       </c>
-      <c r="I251" t="inlineStr"/>
+      <c r="I251" t="n">
+        <v>2010</v>
+      </c>
       <c r="J251" t="inlineStr">
         <is>
           <t>Opioid analgesic</t>
@@ -16190,7 +16296,9 @@
           <t>Sugar spheres; Hypromellose; Ethylcellulose; Macrogol; Povidone; Sucrose</t>
         </is>
       </c>
-      <c r="I254" t="inlineStr"/>
+      <c r="I254" t="n">
+        <v>2013</v>
+      </c>
       <c r="J254" t="inlineStr"/>
       <c r="K254" t="inlineStr"/>
       <c r="L254" t="inlineStr"/>
@@ -16326,7 +16434,9 @@
           <t>microcrystalline cellulose; D-mannitol; sodium starch glycolate; Hypromellose; magnesium stearate; iron oxide black; iron oxide red; macrogol; talc; titanium dioxide</t>
         </is>
       </c>
-      <c r="I256" t="inlineStr"/>
+      <c r="I256" t="n">
+        <v>2020</v>
+      </c>
       <c r="J256" t="inlineStr"/>
       <c r="K256" t="inlineStr"/>
       <c r="L256" t="inlineStr"/>
@@ -16581,7 +16691,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="J260" t="inlineStr"/>
       <c r="K260" t="inlineStr"/>
@@ -16893,7 +17003,9 @@
           <t>Microcrystalline cellulose; Croscarmellose sodium; Lactose anhydrous; Magnesium stearate; Dental type silica; Polyvinyl alcohol; Macrogol 3350; Talc; Titanium dioxide; Iron oxide yellow; Iron oxide red; Shellac; Indigo carmine aluminium lake</t>
         </is>
       </c>
-      <c r="I265" t="inlineStr"/>
+      <c r="I265" t="n">
+        <v>2016</v>
+      </c>
       <c r="J265" t="inlineStr">
         <is>
           <t>Diabetes Mellitus</t>
@@ -16956,7 +17068,9 @@
           <t>Magnesium chloride hexahydrate; Water for injection</t>
         </is>
       </c>
-      <c r="I266" t="inlineStr"/>
+      <c r="I266" t="n">
+        <v>2015</v>
+      </c>
       <c r="J266" t="inlineStr">
         <is>
           <t>Antibacterial agents</t>
@@ -17122,7 +17236,7 @@
       <c r="G269" t="inlineStr"/>
       <c r="H269" t="inlineStr"/>
       <c r="I269" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="J269" t="inlineStr"/>
       <c r="K269" t="inlineStr"/>
@@ -17487,7 +17601,9 @@
           <t>Microcrystalline cellulose; mannitol; povidone K-30; sodium starch glycolate; magnesium stearate; hypromellose; macrogol 400; polysorbate 80; titanium dioxide (E171); Iron oxide Yellow (E-172); Iron oxide Red (E-172)</t>
         </is>
       </c>
-      <c r="I275" t="inlineStr"/>
+      <c r="I275" t="n">
+        <v>2010</v>
+      </c>
       <c r="J275" t="inlineStr">
         <is>
           <t>TPO-R agonist</t>
@@ -17546,7 +17662,9 @@
           <t>microcrystalline cellulose; mannitol; croscarmellose sodium; colloidal anhydrous silica; magnesium stearate; poly(vinyl alcohol); titanium dioxide (E171); macrogol; talc; yellow iron oxide (E172); red iron oxide (E172)</t>
         </is>
       </c>
-      <c r="I276" t="inlineStr"/>
+      <c r="I276" t="n">
+        <v>2025</v>
+      </c>
       <c r="J276" t="inlineStr"/>
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
@@ -17719,7 +17837,9 @@
       </c>
       <c r="G279" t="inlineStr"/>
       <c r="H279" t="inlineStr"/>
-      <c r="I279" t="inlineStr"/>
+      <c r="I279" t="n">
+        <v>2022</v>
+      </c>
       <c r="J279" t="inlineStr"/>
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
@@ -17957,7 +18077,9 @@
         </is>
       </c>
       <c r="H283" t="inlineStr"/>
-      <c r="I283" t="inlineStr"/>
+      <c r="I283" t="n">
+        <v>2017</v>
+      </c>
       <c r="J283" t="inlineStr">
         <is>
           <t>Anticoagulant / Direct factor Xa (FXa) inhibitor</t>
@@ -18016,7 +18138,9 @@
           <t>tartaric acid; lactose anhydrous; hypromellose; crospovidone; microcrystalline cellulose; colloidal anhydrous silica; magnesium stearate; titanium dioxide (E171); yellow iron oxide (E172); sunset yellow FCF (E110); shellac; propylene glycol; indigo carmine aluminium lake (E132)</t>
         </is>
       </c>
-      <c r="I284" t="inlineStr"/>
+      <c r="I284" t="n">
+        <v>2020</v>
+      </c>
       <c r="J284" t="inlineStr">
         <is>
           <t>Anticancer agent</t>
@@ -18144,7 +18268,9 @@
           <t>lactose monohydrate; maize starch; microcrystalline cellulose; low-substituted hydroxypropylcellulose; hydroxypropylcellulose; magnesium stearate; purified water; hypromellose; talc; titanium dioxide; iron oxide E 172</t>
         </is>
       </c>
-      <c r="I286" t="inlineStr"/>
+      <c r="I286" t="n">
+        <v>2018</v>
+      </c>
       <c r="J286" t="inlineStr"/>
       <c r="K286" t="inlineStr"/>
       <c r="L286" t="inlineStr"/>
@@ -18321,7 +18447,9 @@
           <t>lactose monohydrate; mannitol; sodium starch glycolate; hydroxypropyl cellulose; magnesium stearate; hypromellose type 2910; titanium dioxide; triacetin; iron oxide yellow</t>
         </is>
       </c>
-      <c r="I289" t="inlineStr"/>
+      <c r="I289" t="n">
+        <v>2021</v>
+      </c>
       <c r="J289" t="inlineStr"/>
       <c r="K289" t="inlineStr"/>
       <c r="L289" t="inlineStr"/>
@@ -18429,7 +18557,9 @@
           <t>Duro-Tak 387-2287 (pressure sensitive adhesive); Polyethylene terephthalate (backing); Siliconised liner</t>
         </is>
       </c>
-      <c r="I291" t="inlineStr"/>
+      <c r="I291" t="n">
+        <v>2012</v>
+      </c>
       <c r="J291" t="inlineStr">
         <is>
           <t>5-HT3 receptor antagonist</t>
@@ -18744,7 +18874,9 @@
         </is>
       </c>
       <c r="H296" t="inlineStr"/>
-      <c r="I296" t="inlineStr"/>
+      <c r="I296" t="n">
+        <v>2013</v>
+      </c>
       <c r="J296" t="inlineStr">
         <is>
           <t>µ-opioid receptor antagonist</t>
@@ -18803,7 +18935,9 @@
           <t>pregelatinized starch; mannitol (E421); povidone (E1201); sodium starch glycolate Type A; microcrystalline cellulose (E460); colloidal silicon dioxide (E551); magnesium stearate (E578); hypromellose (E464); lactose monohydrate; titanium dioxide (E171); polyethylene glycol (E1521); triacetin (E1518)</t>
         </is>
       </c>
-      <c r="I297" t="inlineStr"/>
+      <c r="I297" t="n">
+        <v>2015</v>
+      </c>
       <c r="J297" t="inlineStr">
         <is>
           <t>Treatment of vulvar and vaginal atrophy</t>
@@ -18912,7 +19046,7 @@
       <c r="G299" t="inlineStr"/>
       <c r="H299" t="inlineStr"/>
       <c r="I299" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="J299" t="inlineStr">
         <is>
@@ -19087,7 +19221,7 @@
         </is>
       </c>
       <c r="I302" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="J302" t="inlineStr">
         <is>
@@ -19151,7 +19285,9 @@
           <t>mannitol; pregelatinised starch; purified water; sodium lauril sulfate; magnesium stearate; gelatine; titanium dioxide; colourants</t>
         </is>
       </c>
-      <c r="I303" t="inlineStr"/>
+      <c r="I303" t="n">
+        <v>2010</v>
+      </c>
       <c r="J303" t="inlineStr">
         <is>
           <t>α1-adrenoreceptor antagonist</t>
@@ -19596,7 +19732,9 @@
           <t>mannitol; microcrystalline cellulose; croscarmellose sodium; colloidal anhydrous silica; magnesium stearate; polyvinyl alcohol; titanium dioxide; macrogol; talc; iron oxide yellow</t>
         </is>
       </c>
-      <c r="I310" t="inlineStr"/>
+      <c r="I310" t="n">
+        <v>2014</v>
+      </c>
       <c r="J310" t="inlineStr"/>
       <c r="K310" t="inlineStr"/>
       <c r="L310" t="inlineStr"/>
@@ -19721,7 +19859,7 @@
         </is>
       </c>
       <c r="I312" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="J312" t="inlineStr"/>
       <c r="K312" t="inlineStr"/>
@@ -20167,7 +20305,9 @@
           <t>macrogol (E1521); water for injections; mannitol (E421); microcrystalline cellulose (E460); croscarmellose sodium (E468); copovidone; magnesium stearate; polyvinyl alcohol (E1203); titanium dioxide (E171); talc (E553b); iron oxide yellow (E172); iron oxide black (E172); iron oxide red (E172)</t>
         </is>
       </c>
-      <c r="I319" t="inlineStr"/>
+      <c r="I319" t="n">
+        <v>2022</v>
+      </c>
       <c r="J319" t="inlineStr">
         <is>
           <t>Antiviral for systemic use, direct acting antivirals, other antivirals (ATC code J05AX31)</t>
@@ -20239,7 +20379,7 @@
         </is>
       </c>
       <c r="I320" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="J320" t="inlineStr">
         <is>
@@ -20303,7 +20443,9 @@
           <t>Gelatin; Mannitol</t>
         </is>
       </c>
-      <c r="I321" t="inlineStr"/>
+      <c r="I321" t="n">
+        <v>2010</v>
+      </c>
       <c r="J321" t="inlineStr">
         <is>
           <t>Atypical antipsychotic</t>
@@ -20573,7 +20715,9 @@
           <t>cellulose microcrystalline; mannitol; crospovidone; povidone; magnesium stearate; silica colloidal anhydrous; sodium laurilsulfate; hypromellose; titanium dioxide (E171); macrogol; talc; iron oxide yellow (E172); iron oxide red (E172); iron oxide black (E172)</t>
         </is>
       </c>
-      <c r="I325" t="inlineStr"/>
+      <c r="I325" t="n">
+        <v>2022</v>
+      </c>
       <c r="J325" t="inlineStr"/>
       <c r="K325" t="inlineStr"/>
       <c r="L325" t="inlineStr"/>
@@ -20612,7 +20756,9 @@
       <c r="F326" t="inlineStr"/>
       <c r="G326" t="inlineStr"/>
       <c r="H326" t="inlineStr"/>
-      <c r="I326" t="inlineStr"/>
+      <c r="I326" t="n">
+        <v>2017</v>
+      </c>
       <c r="J326" t="inlineStr"/>
       <c r="K326" t="inlineStr"/>
       <c r="L326" t="inlineStr"/>
@@ -20728,7 +20874,9 @@
           <t>microcrystalline cellulose; mannitol; low-substituted hydroxpropyl cellulose; sodium stearyl fumarate; polyvinyl alcohol; titanium dioxide (E 171); polyethylene glycol 3350; talc; yellow iron oxide (E 172); red iron oxide (E 172); black iron oxide (E 172)</t>
         </is>
       </c>
-      <c r="I328" t="inlineStr"/>
+      <c r="I328" t="n">
+        <v>2016</v>
+      </c>
       <c r="J328" t="inlineStr"/>
       <c r="K328" t="inlineStr"/>
       <c r="L328" t="inlineStr"/>
@@ -20856,7 +21004,9 @@
           <t>mannitol; sodium hydrogen carbonate; sodium starch glycollate; povidone; magnesium stearate; hypromellose; macrogol 400; titanium dioxide; yellow iron oxide; red iron oxide</t>
         </is>
       </c>
-      <c r="I330" t="inlineStr"/>
+      <c r="I330" t="n">
+        <v>2020</v>
+      </c>
       <c r="J330" t="inlineStr">
         <is>
           <t>Treatment of ITP</t>
@@ -20919,7 +21069,9 @@
           <t>macrogolglycerol hydroxystearate; macrogol (4000); gelatin; red iron oxide (E172); yellow iron oxide (E172); titanium dioxide (E171); polysorbate 80; black iron oxide (E172); shellac; potassium hydroxide</t>
         </is>
       </c>
-      <c r="I331" t="inlineStr"/>
+      <c r="I331" t="n">
+        <v>2022</v>
+      </c>
       <c r="J331" t="inlineStr">
         <is>
           <t>C5aR antagonist</t>
@@ -21052,7 +21204,7 @@
         </is>
       </c>
       <c r="I333" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="J333" t="inlineStr">
         <is>
@@ -21116,7 +21268,9 @@
           <t>silica, hydrophobic colloidal; croscarmellose sodium (E468); hypromellose (E464); lactose monohydrate; magnesium stearate; cellulose, microcrystalline (E460); sodium laurilsulfate (E487); shellac (E904); titanium dioxide (E171); isopropyl alcohol; ammonium hydroxide (E527); butyl alcohol; propylene glycol; simethicone; gelatin; Sunset Yellow (E110)</t>
         </is>
       </c>
-      <c r="I334" t="inlineStr"/>
+      <c r="I334" t="n">
+        <v>2022</v>
+      </c>
       <c r="J334" t="inlineStr"/>
       <c r="K334" t="inlineStr"/>
       <c r="L334" t="inlineStr"/>
@@ -21179,7 +21333,9 @@
           <t>Mannitol; Phosphoric acid</t>
         </is>
       </c>
-      <c r="I335" t="inlineStr"/>
+      <c r="I335" t="n">
+        <v>2015</v>
+      </c>
       <c r="J335" t="inlineStr">
         <is>
           <t>Lipoglycopeptide antibiotic</t>
@@ -21242,7 +21398,9 @@
           <t>mannitol; colloidal anhydrous silica; crospovidone; magnesium stearate; microcrystalline cellulose; hypromellose; lactose monohydrate; macrogol; triacetin; red iron oxide (E172); titanium dioxide (E171)</t>
         </is>
       </c>
-      <c r="I336" t="inlineStr"/>
+      <c r="I336" t="n">
+        <v>2022</v>
+      </c>
       <c r="J336" t="inlineStr"/>
       <c r="K336" t="inlineStr"/>
       <c r="L336" t="inlineStr"/>
@@ -21301,7 +21459,9 @@
           <t>Gelatin; Lactose monohydrate; Magnesium stearate</t>
         </is>
       </c>
-      <c r="I337" t="inlineStr"/>
+      <c r="I337" t="n">
+        <v>2011</v>
+      </c>
       <c r="J337" t="inlineStr">
         <is>
           <t>Oncology</t>
@@ -21482,7 +21642,9 @@
           <t>mannitol (E421); microcrystalline cellulose; povidone; sodium starch glycollate; sodium stearyl fumarate; polyvinyl alcohol-part hydrolyzed; titanium dioxide (E171); macrogol; talc; iron oxide yellow (E172)</t>
         </is>
       </c>
-      <c r="I340" t="inlineStr"/>
+      <c r="I340" t="n">
+        <v>2014</v>
+      </c>
       <c r="J340" t="inlineStr">
         <is>
           <t>Integrase inhibitor</t>
@@ -21545,7 +21707,9 @@
           <t>Sulphuric acid; 1, 2-distearoyl-sn-glycerol-3-phosphocholine (DSPC); Calcium chloride; Hypromellose; Carrageenan (E407); Potassium chloride; Printing ink (blue); Carnauba wax</t>
         </is>
       </c>
-      <c r="I341" t="inlineStr"/>
+      <c r="I341" t="n">
+        <v>2011</v>
+      </c>
       <c r="J341" t="inlineStr">
         <is>
           <t>Antibiotics</t>
@@ -21791,7 +21955,9 @@
           <t>mannitol; pregelatinised starch; maize starch; copovidone; magnesium stearate; hypromellose; titanium dioxide; talc; macrogol 6000; red iron oxide</t>
         </is>
       </c>
-      <c r="I345" t="inlineStr"/>
+      <c r="I345" t="n">
+        <v>2011</v>
+      </c>
       <c r="J345" t="inlineStr">
         <is>
           <t>Treatment of type 2 diabetes mellitus</t>
@@ -21915,7 +22081,9 @@
           <t>ethanol anhydrous; hydrochloric acid; norflurane</t>
         </is>
       </c>
-      <c r="I347" t="inlineStr"/>
+      <c r="I347" t="n">
+        <v>2017</v>
+      </c>
       <c r="J347" t="inlineStr">
         <is>
           <t>Chronic Obstructive Pulmonary Disease (COPD)</t>
@@ -22165,7 +22333,9 @@
           <t>microcrystalline cellulose (E460i); dibasic calcium phosphate; croscarmellose sodium (E468); magnesium stearate (E470b); hypromellose; titanium dioxide (E171); macrogol 3350; polydextrose; copovidone; medium-chain triglycerides; black iron oxide (E172); red iron oxide (E172); yellow and iron oxide (E172)</t>
         </is>
       </c>
-      <c r="I351" t="inlineStr"/>
+      <c r="I351" t="n">
+        <v>2024</v>
+      </c>
       <c r="J351" t="inlineStr">
         <is>
           <t>Anticancer</t>
@@ -22415,7 +22585,9 @@
           <t>microcrystalline cellulose; silicon dioxide; croscarmellose sodium; magnesium stearate; sunset yellow FCF (FD&amp;C yellow #6) aluminium lake (E110); polyethylene glycol; polyvinyl alcohol; talc (E553B); titanium dioxide (E171); iron oxide yellow (E172)</t>
         </is>
       </c>
-      <c r="I355" t="inlineStr"/>
+      <c r="I355" t="n">
+        <v>2013</v>
+      </c>
       <c r="J355" t="inlineStr">
         <is>
           <t>Pharmacokinetic enhancer</t>
@@ -22466,7 +22638,9 @@
       </c>
       <c r="G356" t="inlineStr"/>
       <c r="H356" t="inlineStr"/>
-      <c r="I356" t="inlineStr"/>
+      <c r="I356" t="n">
+        <v>2014</v>
+      </c>
       <c r="J356" t="inlineStr">
         <is>
           <t>Adrenergics in combination with anticholinergic</t>
@@ -22590,7 +22764,9 @@
           <t>mannitol; pregelatinised starch; purified water; sodium lauril sulfate; magnesium stearate; gelatine; titanium dioxide; colourants</t>
         </is>
       </c>
-      <c r="I358" t="inlineStr"/>
+      <c r="I358" t="n">
+        <v>2010</v>
+      </c>
       <c r="J358" t="inlineStr"/>
       <c r="K358" t="inlineStr"/>
       <c r="L358" t="inlineStr"/>
@@ -22779,7 +22955,9 @@
           <t>sodium chloride; calcium chloride; magnesium sulphate; water for injection; sulphuric acid; sodium hydroxide</t>
         </is>
       </c>
-      <c r="I361" t="inlineStr"/>
+      <c r="I361" t="n">
+        <v>2019</v>
+      </c>
       <c r="J361" t="inlineStr"/>
       <c r="K361" t="inlineStr"/>
       <c r="L361" t="inlineStr"/>
@@ -23270,7 +23448,7 @@
         </is>
       </c>
       <c r="I369" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="J369" t="inlineStr"/>
       <c r="K369" t="inlineStr"/>
@@ -23460,7 +23638,9 @@
           <t>Medium-chain triglycerides; Cetalkonium chloride; Glycerol; Tyloxapol; Poloxamer 188; Sodium hydroxide; Water for injections</t>
         </is>
       </c>
-      <c r="I372" t="inlineStr"/>
+      <c r="I372" t="n">
+        <v>2018</v>
+      </c>
       <c r="J372" t="inlineStr"/>
       <c r="K372" t="inlineStr"/>
       <c r="L372" t="inlineStr"/>
@@ -23707,7 +23887,7 @@
         </is>
       </c>
       <c r="I376" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="J376" t="inlineStr">
         <is>
@@ -24620,7 +24800,9 @@
           <t>gelatin; glycerine; sorbitol liquid (E420); titanium dioxide (E171); purified water; polyethylene glycol 400; sorbitan monooleate; polysorbate 80; opacode Black; n-Butyl alcohol; propylene glycol; d-sorbitol; 1,4 sorbitan; mannitol</t>
         </is>
       </c>
-      <c r="I390" t="inlineStr"/>
+      <c r="I390" t="n">
+        <v>2011</v>
+      </c>
       <c r="J390" t="inlineStr">
         <is>
           <t>TTR tetramer stabiliser</t>
@@ -24683,7 +24865,9 @@
           <t>microcrystalline cellulose; crospovidone Type A; talc; magnesium stearate; colloidal anhydrous silica; polyvinyl alcohol; titanium dioxide (E171); macrogol 3350</t>
         </is>
       </c>
-      <c r="I391" t="inlineStr"/>
+      <c r="I391" t="n">
+        <v>2016</v>
+      </c>
       <c r="J391" t="inlineStr"/>
       <c r="K391" t="inlineStr"/>
       <c r="L391" t="inlineStr"/>
@@ -24743,7 +24927,7 @@
         </is>
       </c>
       <c r="I392" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="J392" t="inlineStr">
         <is>
@@ -24929,7 +25113,9 @@
           <t>hypromellose acetate succinate; cellulose microcrystalline (E460); mannitol (E421); croscarmellose sodium (E468); silica, colloidal anhydrous (E551); magnesium stearate (E470b); polyvinyl alcohol (E1203); titanium dioxide (E171); macrogol (E1521); talc (E553b); indigo carmine aluminium lake (E132)</t>
         </is>
       </c>
-      <c r="I395" t="inlineStr"/>
+      <c r="I395" t="n">
+        <v>2025</v>
+      </c>
       <c r="J395" t="inlineStr"/>
       <c r="K395" t="inlineStr">
         <is>
@@ -24996,7 +25182,9 @@
           <t>microcrystalline cellulose; crospovidone type A; magnesium stearate; colloidal anhydrous silica; hypromellose; polyethylene glycol 6000; titanium dioxide (E171); iron oxide red (E172); mica (E555)</t>
         </is>
       </c>
-      <c r="I396" t="inlineStr"/>
+      <c r="I396" t="n">
+        <v>2015</v>
+      </c>
       <c r="J396" t="inlineStr">
         <is>
           <t>Anti-Parkinson's disease therapy (MAO-B inhibitor)</t>
@@ -25059,7 +25247,9 @@
           <t>Gelatin</t>
         </is>
       </c>
-      <c r="I397" t="inlineStr"/>
+      <c r="I397" t="n">
+        <v>2012</v>
+      </c>
       <c r="J397" t="inlineStr">
         <is>
           <t>ALK receptor tyrosine kinase inhibitor</t>
@@ -25118,7 +25308,9 @@
           <t>Xanthan gum; Aspartame; Concentrated raspberry juice; Sucrose; Sulphur dioxide; Methyl parahydroxybenzoate; Propyl parahydroxybenzoate; Water</t>
         </is>
       </c>
-      <c r="I398" t="inlineStr"/>
+      <c r="I398" t="n">
+        <v>2012</v>
+      </c>
       <c r="J398" t="inlineStr"/>
       <c r="K398" t="inlineStr"/>
       <c r="L398" t="inlineStr"/>
@@ -25177,7 +25369,9 @@
           <t>microcrystalline cellulose; lactose monohydrate; croscarmellose sodium; magnesium stearate; hypromellose 6cP (E464); titanium dioxide (E171); macrogol 3350; triacetin (E1518)</t>
         </is>
       </c>
-      <c r="I399" t="inlineStr"/>
+      <c r="I399" t="n">
+        <v>2017</v>
+      </c>
       <c r="J399" t="inlineStr">
         <is>
           <t>Rheumatoid Arthritis</t>
@@ -25370,7 +25564,9 @@
           <t>hydroxypropylcellulose; microcrystalline cellulose; magnesium stearate; sodium starch glycollate type A; polyvinyl alcohol; macrogol 3350; talc; titanium dioxide; iron oxide yellow; iron oxide red</t>
         </is>
       </c>
-      <c r="I402" t="inlineStr"/>
+      <c r="I402" t="n">
+        <v>2014</v>
+      </c>
       <c r="J402" t="inlineStr">
         <is>
           <t>Oral antidiabetic</t>
@@ -25434,7 +25630,7 @@
         </is>
       </c>
       <c r="I403" t="n">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="J403" t="inlineStr">
         <is>
@@ -25556,7 +25752,7 @@
         </is>
       </c>
       <c r="I405" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="J405" t="inlineStr">
         <is>
@@ -26055,7 +26251,9 @@
           <t>trometamol; sodium chloride; water for injections; hydrochloric acid; sodium hydroxide</t>
         </is>
       </c>
-      <c r="I413" t="inlineStr"/>
+      <c r="I413" t="n">
+        <v>2024</v>
+      </c>
       <c r="J413" t="inlineStr">
         <is>
           <t>Antihypoglycaemic</t>
@@ -26183,7 +26381,9 @@
           <t>Colloidal anhydrous silica; Croscarmellose sodium; Hydroxypropylcellulose; Magnesium stearate; Hydroxypropyl methylcellulose acetate succinate (HPMC-AS)</t>
         </is>
       </c>
-      <c r="I415" t="inlineStr"/>
+      <c r="I415" t="n">
+        <v>2012</v>
+      </c>
       <c r="J415" t="inlineStr"/>
       <c r="K415" t="inlineStr">
         <is>
@@ -26457,7 +26657,9 @@
           <t>Lactose</t>
         </is>
       </c>
-      <c r="I419" t="inlineStr"/>
+      <c r="I419" t="n">
+        <v>2011</v>
+      </c>
       <c r="J419" t="inlineStr">
         <is>
           <t>Hormonal contraceptives for systemic use - progestagens and estrogens, fixed combinations</t>
@@ -26654,7 +26856,9 @@
           <t>mannitol; citric acid anhydrous; sodium citrate; microcrystalline cellulose; croscarmellose sodium; sucralose; levomenthol; colloidal anhydrous silica; sodium stearyl fumarate</t>
         </is>
       </c>
-      <c r="I422" t="inlineStr"/>
+      <c r="I422" t="n">
+        <v>2017</v>
+      </c>
       <c r="J422" t="inlineStr">
         <is>
           <t>Treatment of opioid dependence</t>
@@ -26839,7 +27043,9 @@
           <t>Lactose monohydrate; microcrystalline cellulose; croscarmellose sodium; povidone; sodium lauryl sulfate; magnesium stearate; colloidal silicon dioxide</t>
         </is>
       </c>
-      <c r="I425" t="inlineStr"/>
+      <c r="I425" t="n">
+        <v>2011</v>
+      </c>
       <c r="J425" t="inlineStr">
         <is>
           <t>Prostate cancer</t>
@@ -27362,7 +27568,9 @@
       </c>
       <c r="G436" t="inlineStr"/>
       <c r="H436" t="inlineStr"/>
-      <c r="I436" t="inlineStr"/>
+      <c r="I436" t="n">
+        <v>2014</v>
+      </c>
       <c r="J436" t="inlineStr">
         <is>
           <t>Treatment of epilepsy, neuropathic pain and Generalised Anxiety Disorder</t>
@@ -27486,7 +27694,9 @@
         </is>
       </c>
       <c r="H438" t="inlineStr"/>
-      <c r="I438" t="inlineStr"/>
+      <c r="I438" t="n">
+        <v>2012</v>
+      </c>
       <c r="J438" t="inlineStr">
         <is>
           <t>Treatment of amyotrophic lateral sclerosis (ALS)</t>
@@ -27533,7 +27743,9 @@
       <c r="F439" t="inlineStr"/>
       <c r="G439" t="inlineStr"/>
       <c r="H439" t="inlineStr"/>
-      <c r="I439" t="inlineStr"/>
+      <c r="I439" t="n">
+        <v>2010</v>
+      </c>
       <c r="J439" t="inlineStr">
         <is>
           <t>Dipeptidyl peptidase-4 (DPP-4) inhibitor</t>
@@ -27584,7 +27796,9 @@
       </c>
       <c r="G440" t="inlineStr"/>
       <c r="H440" t="inlineStr"/>
-      <c r="I440" t="inlineStr"/>
+      <c r="I440" t="n">
+        <v>2010</v>
+      </c>
       <c r="J440" t="inlineStr">
         <is>
           <t>A10BD07 / Oral blood glucose-lowering drugs</t>
@@ -27627,7 +27841,9 @@
       <c r="F441" t="inlineStr"/>
       <c r="G441" t="inlineStr"/>
       <c r="H441" t="inlineStr"/>
-      <c r="I441" t="inlineStr"/>
+      <c r="I441" t="n">
+        <v>2013</v>
+      </c>
       <c r="J441" t="inlineStr"/>
       <c r="K441" t="inlineStr"/>
       <c r="L441" t="inlineStr"/>
@@ -27666,7 +27882,9 @@
       <c r="F442" t="inlineStr"/>
       <c r="G442" t="inlineStr"/>
       <c r="H442" t="inlineStr"/>
-      <c r="I442" t="inlineStr"/>
+      <c r="I442" t="n">
+        <v>2018</v>
+      </c>
       <c r="J442" t="inlineStr"/>
       <c r="K442" t="inlineStr"/>
       <c r="L442" t="inlineStr"/>
@@ -29349,7 +29567,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -29697,7 +29915,9 @@
           <t>Microcrystalline cellulose; Lactose monohydrate; Croscarmellose sodium; Sodium lauryl sulphate; Colloidal silicon dioxide; Magnesium stearate; Carnauba wax; Hypromellose acetate succinate (HPMCAS); Opadry II Blue; Opacode Black</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="n">
+        <v>2012</v>
+      </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
@@ -29764,7 +29984,9 @@
           <t>microcrystalline cellulose; croscarmellose sodium; hypromellose acetate succinate; povidone K30; sodium laurilsulfate; magnesium stearate; polyvinyl alcohol; titanium dioxide (E171); macrogol 3350; talc; carmine (E120); brilliant blue FCF aluminum lake (E133); indigo carmine aluminum lake (E132); shellac; iron oxide black (E172); propylene glycol; ammonium hydroxide; carnauba wax</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="n">
+        <v>2015</v>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>CFTR corrector and potentiator</t>
@@ -30192,7 +30414,9 @@
           <t>macrogol (E1521); water for injections; mannitol (E421); microcrystalline cellulose (E460); croscarmellose sodium (E468); copovidone; magnesium stearate; polyvinyl alcohol (E1203); titanium dioxide (E171); talc (E553b); iron oxide yellow (E172); iron oxide black (E172); iron oxide red (E172)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="n">
+        <v>2022</v>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
           <t>Antiviral for systemic use, direct acting antivirals, other antivirals (ATC code J05AX31)</t>
@@ -30336,7 +30560,9 @@
           <t>macrogolglycerol hydroxystearate; macrogol (4000); gelatin; red iron oxide (E172); yellow iron oxide (E172); titanium dioxide (E171); polysorbate 80; black iron oxide (E172); shellac; potassium hydroxide</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="n">
+        <v>2022</v>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
           <t>C5aR antagonist</t>
@@ -30825,7 +31051,9 @@
           <t>hypromellose acetate succinate; cellulose microcrystalline (E460); mannitol (E421); croscarmellose sodium (E468); silica, colloidal anhydrous (E551); magnesium stearate (E470b); polyvinyl alcohol (E1203); titanium dioxide (E171); macrogol (E1521); talc (E553b); indigo carmine aluminium lake (E132)</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="n">
+        <v>2025</v>
+      </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
@@ -30892,7 +31120,9 @@
           <t>Colloidal anhydrous silica; Croscarmellose sodium; Hydroxypropylcellulose; Magnesium stearate; Hydroxypropyl methylcellulose acetate succinate (HPMC-AS)</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="n">
+        <v>2012</v>
+      </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
